--- a/全量数据/SPDR黄金ETF份额.xlsx
+++ b/全量数据/SPDR黄金ETF份额.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPDR黄金ETF行情" sheetId="1" r:id="R1af383100de44963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPDR黄金ETF行情" sheetId="1" r:id="Re0749f9150044126"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32522,6 +32522,26 @@
         <x:v>365396468.580051</x:v>
       </x:c>
     </x:row>
+    <x:row r="1607">
+      <x:c r="A1607" s="2" t="d">
+        <x:v>2026-10-26T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B1607" s="3" t="n">
+        <x:v>367.82</x:v>
+      </x:c>
+      <x:c r="C1607" s="4" t="n">
+        <x:v>0.00000285067719358752</x:v>
+      </x:c>
+      <x:c r="D1607" s="5" t="n">
+        <x:v>6548104</x:v>
+      </x:c>
+      <x:c r="E1607" s="6" t="n">
+        <x:v>1040.8</x:v>
+      </x:c>
+      <x:c r="F1607" s="7" t="n">
+        <x:v>365108229.6615218</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/全量数据/SPDR黄金ETF份额.xlsx
+++ b/全量数据/SPDR黄金ETF份额.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPDR黄金ETF行情" sheetId="1" r:id="Re0749f9150044126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPDR黄金ETF行情" sheetId="1" r:id="Redfb0a5566d74db1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32542,6 +32542,26 @@
         <x:v>365108229.6615218</x:v>
       </x:c>
     </x:row>
+    <x:row r="1608">
+      <x:c r="A1608" s="2" t="d">
+        <x:v>2026-10-27T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B1608" s="3" t="n">
+        <x:v>372.28</x:v>
+      </x:c>
+      <x:c r="C1608" s="4" t="n">
+        <x:v>0.000002850652932875616</x:v>
+      </x:c>
+      <x:c r="D1608" s="5" t="n">
+        <x:v>5335889</x:v>
+      </x:c>
+      <x:c r="E1608" s="6" t="n">
+        <x:v>1041.65</x:v>
+      </x:c>
+      <x:c r="F1608" s="7" t="n">
+        <x:v>365411336.98822767</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/全量数据/SPDR黄金ETF份额.xlsx
+++ b/全量数据/SPDR黄金ETF份额.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPDR黄金ETF行情" sheetId="1" r:id="Redfb0a5566d74db1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPDR黄金ETF行情" sheetId="1" r:id="Re1112d17379c4064"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32562,6 +32562,26 @@
         <x:v>365411336.98822767</x:v>
       </x:c>
     </x:row>
+    <x:row r="1609">
+      <x:c r="A1609" s="2" t="d">
+        <x:v>2026-10-28T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B1609" s="3" t="n">
+        <x:v>373.51</x:v>
+      </x:c>
+      <x:c r="C1609" s="4" t="n">
+        <x:v>0.000002850618408016368</x:v>
+      </x:c>
+      <x:c r="D1609" s="5" t="n">
+        <x:v>9013109</x:v>
+      </x:c>
+      <x:c r="E1609" s="6" t="n">
+        <x:v>1043.36</x:v>
+      </x:c>
+      <x:c r="F1609" s="7" t="n">
+        <x:v>366015762.6592875</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/全量数据/SPDR黄金ETF份额.xlsx
+++ b/全量数据/SPDR黄金ETF份额.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPDR黄金ETF行情" sheetId="1" r:id="Re1112d17379c4064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPDR黄金ETF行情" sheetId="1" r:id="R597601cef86a4c18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32582,6 +32582,26 @@
         <x:v>366015762.6592875</x:v>
       </x:c>
     </x:row>
+    <x:row r="1610">
+      <x:c r="A1610" s="2" t="d">
+        <x:v>2026-10-29T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B1610" s="3" t="n">
+        <x:v>368.57</x:v>
+      </x:c>
+      <x:c r="C1610" s="4" t="n">
+        <x:v>0.00000285058388315712</x:v>
+      </x:c>
+      <x:c r="D1610" s="5" t="n">
+        <x:v>9132565</x:v>
+      </x:c>
+      <x:c r="E1610" s="6" t="n">
+        <x:v>1041.08</x:v>
+      </x:c>
+      <x:c r="F1610" s="7" t="n">
+        <x:v>365220195.660808</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
